--- a/template_siswa_tabel_D4DA6B98FCFD71C58F5A_2024 (1).xlsx
+++ b/template_siswa_tabel_D4DA6B98FCFD71C58F5A_2024 (1).xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="10230" yWindow="-15" windowWidth="10275" windowHeight="8160"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
@@ -5022,7 +5022,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5032,6 +5032,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4F81BD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -5047,13 +5053,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5514,79 +5523,79 @@
       <c r="A3">
         <v>12</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="4">
         <v>22230147</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="M3" t="s">
+      <c r="M3" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="N3" t="s">
+      <c r="N3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="O3" t="s">
+      <c r="O3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="P3" t="s">
+      <c r="P3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="Q3" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="R3" t="s">
+      <c r="R3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="S3" t="s">
+      <c r="S3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="T3" t="s">
+      <c r="T3" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="U3" t="s">
+      <c r="U3" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="V3">
+      <c r="V3" s="4">
         <v>10</v>
       </c>
-      <c r="W3" t="s">
+      <c r="W3" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="X3" t="s">
+      <c r="X3" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="Y3" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="Z3" t="s">
+      <c r="Z3" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AA3" t="s">
@@ -5601,79 +5610,79 @@
       <c r="A4">
         <v>12</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="4">
         <v>22230148</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="L4" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="M4" t="s">
+      <c r="M4" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="N4" t="s">
+      <c r="N4" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="O4" t="s">
+      <c r="O4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="P4" t="s">
+      <c r="P4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="Q4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="R4" t="s">
+      <c r="R4" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="S4" t="s">
+      <c r="S4" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="T4" t="s">
+      <c r="T4" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="U4" t="s">
+      <c r="U4" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="V4">
+      <c r="V4" s="4">
         <v>10</v>
       </c>
-      <c r="W4" t="s">
+      <c r="W4" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="X4" t="s">
+      <c r="X4" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="Y4" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="Z4" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AA4" t="s">
@@ -5688,79 +5697,79 @@
       <c r="A5">
         <v>12</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="4">
         <v>22230031</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="K5" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="L5" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="M5" t="s">
+      <c r="M5" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="N5" t="s">
+      <c r="N5" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="O5" t="s">
+      <c r="O5" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="P5" t="s">
+      <c r="P5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="Q5" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="R5" t="s">
+      <c r="R5" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="S5" t="s">
+      <c r="S5" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="T5" t="s">
+      <c r="T5" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="U5" t="s">
+      <c r="U5" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="V5">
+      <c r="V5" s="4">
         <v>10</v>
       </c>
-      <c r="W5" t="s">
+      <c r="W5" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="X5" t="s">
+      <c r="X5" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="Y5" t="s">
+      <c r="Y5" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="Z5" t="s">
+      <c r="Z5" s="4" t="s">
         <v>101</v>
       </c>
       <c r="AA5" t="s">
@@ -5775,79 +5784,79 @@
       <c r="A6">
         <v>12</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="4">
         <v>23240001</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="K6" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="L6" s="2" t="s">
+      <c r="L6" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="M6" t="s">
+      <c r="M6" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="N6" t="s">
+      <c r="N6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="O6" t="s">
+      <c r="O6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="P6" t="s">
+      <c r="P6" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="Q6" t="s">
+      <c r="Q6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="R6" t="s">
+      <c r="R6" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="S6" t="s">
+      <c r="S6" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="T6" t="s">
+      <c r="T6" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="U6" t="s">
+      <c r="U6" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="V6">
+      <c r="V6" s="4">
         <v>10</v>
       </c>
-      <c r="W6" t="s">
+      <c r="W6" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="X6" t="s">
+      <c r="X6" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="Y6" t="s">
+      <c r="Y6" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="Z6" t="s">
+      <c r="Z6" s="4" t="s">
         <v>111</v>
       </c>
       <c r="AA6" t="s">
@@ -5862,79 +5871,79 @@
       <c r="A7">
         <v>12</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="4">
         <v>21220189</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I7" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="J7" t="s">
+      <c r="J7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="K7" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="L7" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="M7" t="s">
+      <c r="M7" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="N7" t="s">
+      <c r="N7" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="O7" t="s">
+      <c r="O7" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="P7" t="s">
+      <c r="P7" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="Q7" t="s">
+      <c r="Q7" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="R7" t="s">
+      <c r="R7" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="S7" t="s">
+      <c r="S7" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="T7" t="s">
+      <c r="T7" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="U7" t="s">
+      <c r="U7" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="V7">
+      <c r="V7" s="4">
         <v>10</v>
       </c>
-      <c r="W7" t="s">
+      <c r="W7" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="X7" t="s">
+      <c r="X7" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="Y7" t="s">
+      <c r="Y7" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="Z7" t="s">
+      <c r="Z7" s="4" t="s">
         <v>120</v>
       </c>
       <c r="AA7" t="s">
@@ -5949,79 +5958,79 @@
       <c r="A8">
         <v>12</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="4">
         <v>21220104</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="I8" t="s">
+      <c r="I8" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="K8" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="L8" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="M8" t="s">
+      <c r="M8" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="N8" t="s">
+      <c r="N8" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="O8" t="s">
+      <c r="O8" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="P8" t="s">
+      <c r="P8" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="Q8" t="s">
+      <c r="Q8" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="R8" t="s">
+      <c r="R8" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="S8" t="s">
+      <c r="S8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="T8" t="s">
+      <c r="T8" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="U8" t="s">
+      <c r="U8" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="V8">
+      <c r="V8" s="4">
         <v>10</v>
       </c>
-      <c r="W8" t="s">
+      <c r="W8" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="X8" t="s">
+      <c r="X8" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="Y8" t="s">
+      <c r="Y8" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="Z8" t="s">
+      <c r="Z8" s="4" t="s">
         <v>129</v>
       </c>
       <c r="AA8" t="s">
